--- a/public/models/Budget_vs_Actual_Model_AagamJain.xlsx
+++ b/public/models/Budget_vs_Actual_Model_AagamJain.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="0"/>
@@ -97,21 +97,6 @@
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="18"/>
-    </font>
-    <font>
-      <name val=""/>
-      <charset val="1"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val=""/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="11">
@@ -963,11 +948,11 @@
         </ser>
         <gapWidth val="164"/>
         <overlap val="-22"/>
-        <axId val="37756846"/>
-        <axId val="98051195"/>
+        <axId val="76758311"/>
+        <axId val="95391719"/>
       </barChart>
       <catAx>
-        <axId val="37756846"/>
+        <axId val="76758311"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
@@ -1003,7 +988,7 @@
             </a:r>
           </a:p>
         </txPr>
-        <crossAx val="98051195"/>
+        <crossAx val="95391719"/>
         <crossesAt val="0"/>
         <auto val="1"/>
         <lblAlgn val="ctr"/>
@@ -1011,7 +996,7 @@
         <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
-        <axId val="98051195"/>
+        <axId val="95391719"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
@@ -1044,7 +1029,7 @@
             </a:r>
           </a:p>
         </txPr>
-        <crossAx val="37756846"/>
+        <crossAx val="76758311"/>
         <crosses val="min"/>
         <crossBetween val="between"/>
       </valAx>
@@ -1059,8 +1044,6 @@
           <hMode val="factor"/>
           <x val="0.786405547512002"/>
           <y val="0.171202933295727"/>
-          <w val="0.187547629934461"/>
-          <h val="0.08377997179125531"/>
         </manualLayout>
       </layout>
       <overlay val="0"/>
@@ -1430,11 +1413,11 @@
         </ser>
         <gapWidth val="164"/>
         <overlap val="-22"/>
-        <axId val="73803618"/>
-        <axId val="15466456"/>
+        <axId val="78033605"/>
+        <axId val="35567914"/>
       </barChart>
       <catAx>
-        <axId val="73803618"/>
+        <axId val="78033605"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
@@ -1515,7 +1498,7 @@
             </a:r>
           </a:p>
         </txPr>
-        <crossAx val="15466456"/>
+        <crossAx val="35567914"/>
         <crossesAt val="0"/>
         <auto val="1"/>
         <lblAlgn val="ctr"/>
@@ -1523,7 +1506,7 @@
         <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
-        <axId val="15466456"/>
+        <axId val="35567914"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
@@ -1556,7 +1539,7 @@
             </a:r>
           </a:p>
         </txPr>
-        <crossAx val="73803618"/>
+        <crossAx val="78033605"/>
         <crosses val="min"/>
         <crossBetween val="between"/>
       </valAx>
@@ -1570,9 +1553,7 @@
           <wMode val="factor"/>
           <hMode val="factor"/>
           <x val="0.378237214363439"/>
-          <y val="0.8794299876084259"/>
-          <w val="0.224318049912943"/>
-          <h val="0.0736150700210683"/>
+          <y val="0.852416356877323"/>
         </manualLayout>
       </layout>
       <overlay val="0"/>
@@ -1936,11 +1917,11 @@
         </ser>
         <gapWidth val="164"/>
         <overlap val="-22"/>
-        <axId val="67969094"/>
-        <axId val="47317447"/>
+        <axId val="98215784"/>
+        <axId val="73593409"/>
       </barChart>
       <catAx>
-        <axId val="67969094"/>
+        <axId val="98215784"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
@@ -2021,7 +2002,7 @@
             </a:r>
           </a:p>
         </txPr>
-        <crossAx val="47317447"/>
+        <crossAx val="73593409"/>
         <crossesAt val="0"/>
         <auto val="1"/>
         <lblAlgn val="ctr"/>
@@ -2029,7 +2010,7 @@
         <noMultiLvlLbl val="0"/>
       </catAx>
       <valAx>
-        <axId val="47317447"/>
+        <axId val="73593409"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
@@ -2073,7 +2054,7 @@
             </a:r>
           </a:p>
         </txPr>
-        <crossAx val="67969094"/>
+        <crossAx val="98215784"/>
         <crosses val="min"/>
         <crossBetween val="between"/>
       </valAx>
@@ -2087,9 +2068,7 @@
           <wMode val="factor"/>
           <hMode val="factor"/>
           <x val="0.31503937007874"/>
-          <y val="0.893493520518359"/>
-          <w val="0.353256161902512"/>
-          <h val="0.07803429188605369"/>
+          <y val="0.839362850971922"/>
         </manualLayout>
       </layout>
       <overlay val="0"/>
@@ -2538,14 +2517,6 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="1">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -3612,21 +3583,12 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="1">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
-    <tabColor rgb="FF002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -3980,14 +3942,6 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="1">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -3995,7 +3949,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
-    <tabColor rgb="FF002060"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -4453,14 +4406,6 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="1">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -4468,7 +4413,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
-    <tabColor rgb="FFA90F1A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
@@ -4658,14 +4602,6 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="1">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -6017,14 +5953,6 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="1">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -11568,13 +11496,5 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentOddEven="0" differentFirst="1">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>